--- a/trades.xlsx
+++ b/trades.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JoaquinGarciaAiello\Desktop\Repository\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64FBD856-A050-4E38-8A90-C33121310038}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D93DE05-78E0-49FA-8CDF-14F8FD248EED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,30 +36,54 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="16">
   <si>
     <t>TradeId</t>
   </si>
   <si>
-    <t>T107176-01</t>
-  </si>
-  <si>
     <t>T106729-01</t>
   </si>
   <si>
-    <t>T109055-01</t>
-  </si>
-  <si>
     <t>T106749-01</t>
   </si>
   <si>
-    <t>T108150-01</t>
-  </si>
-  <si>
-    <t>T108198-01</t>
-  </si>
-  <si>
-    <t>T108151-01</t>
+    <t>T004521-01</t>
+  </si>
+  <si>
+    <t>T004724-01</t>
+  </si>
+  <si>
+    <t>T004572-01</t>
+  </si>
+  <si>
+    <t>T004563-01</t>
+  </si>
+  <si>
+    <t>T004676-01</t>
+  </si>
+  <si>
+    <t>T004675-01</t>
+  </si>
+  <si>
+    <t>T004678-01</t>
+  </si>
+  <si>
+    <t>T004457-01</t>
+  </si>
+  <si>
+    <t>T004483-01</t>
+  </si>
+  <si>
+    <t>T004485-01</t>
+  </si>
+  <si>
+    <t>T004488-01</t>
+  </si>
+  <si>
+    <t>T004437-01</t>
+  </si>
+  <si>
+    <t>T004440-01</t>
   </si>
 </sst>
 </file>
@@ -407,17 +431,17 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
@@ -427,17 +451,87 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="1684" spans="1:1" x14ac:dyDescent="0.25">

--- a/trades.xlsx
+++ b/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A23"/>
+  <dimension ref="A1:A21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,91 +489,77 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>T004678-01</t>
+          <t>T004457-01</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>T004457-01</t>
+          <t>T004483-01</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>T004483-01</t>
+          <t>T004485-01</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>T004485-01</t>
+          <t>T004488-01</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>T004488-01</t>
+          <t>T004437-01</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>T004437-01</t>
+          <t>T004440-01</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>T004440-01</t>
+          <t>T004521-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T004521-01</t>
+          <t>T004572-01</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>T004572-01</t>
+          <t>T004724-01</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>T004724-01</t>
+          <t>T004437-01</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>T004437-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
           <t>T004440-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>T004441-01</t>
         </is>
       </c>
     </row>

--- a/trades.xlsx
+++ b/trades.xlsx
@@ -1,37 +1,380 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JoaquinGarciaAiello\Desktop\Repository\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8D21465-2A77-4A3D-886B-E15BAED4FAE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="105">
+  <si>
+    <t>TradeId</t>
+  </si>
+  <si>
+    <t>T127619-01</t>
+  </si>
+  <si>
+    <t>T125909-01</t>
+  </si>
+  <si>
+    <t>T127799-01</t>
+  </si>
+  <si>
+    <t>T127800-01</t>
+  </si>
+  <si>
+    <t>T127901-01</t>
+  </si>
+  <si>
+    <t>T127903-01</t>
+  </si>
+  <si>
+    <t>T127951-01</t>
+  </si>
+  <si>
+    <t>T121839-01</t>
+  </si>
+  <si>
+    <t>T127972-01</t>
+  </si>
+  <si>
+    <t>T128012-01</t>
+  </si>
+  <si>
+    <t>T128013-01</t>
+  </si>
+  <si>
+    <t>T124825-01</t>
+  </si>
+  <si>
+    <t>T128019-01</t>
+  </si>
+  <si>
+    <t>T128020-01</t>
+  </si>
+  <si>
+    <t>T128021-01</t>
+  </si>
+  <si>
+    <t>T128039-01</t>
+  </si>
+  <si>
+    <t>T128041-01</t>
+  </si>
+  <si>
+    <t>T121992-01</t>
+  </si>
+  <si>
+    <t>T128056-01</t>
+  </si>
+  <si>
+    <t>T128057-01</t>
+  </si>
+  <si>
+    <t>T128058-01</t>
+  </si>
+  <si>
+    <t>T121194-01</t>
+  </si>
+  <si>
+    <t>T121208-01</t>
+  </si>
+  <si>
+    <t>T121256-01</t>
+  </si>
+  <si>
+    <t>T121451-01</t>
+  </si>
+  <si>
+    <t>T121498-01</t>
+  </si>
+  <si>
+    <t>T121519-01</t>
+  </si>
+  <si>
+    <t>T121669-01</t>
+  </si>
+  <si>
+    <t>T121725-01</t>
+  </si>
+  <si>
+    <t>T121761-01</t>
+  </si>
+  <si>
+    <t>T121766-01</t>
+  </si>
+  <si>
+    <t>T121837-01</t>
+  </si>
+  <si>
+    <t>T121846-01</t>
+  </si>
+  <si>
+    <t>T121858-01</t>
+  </si>
+  <si>
+    <t>T121926-01</t>
+  </si>
+  <si>
+    <t>T121927-01</t>
+  </si>
+  <si>
+    <t>T121960-01</t>
+  </si>
+  <si>
+    <t>T122031-01</t>
+  </si>
+  <si>
+    <t>T122035-01</t>
+  </si>
+  <si>
+    <t>T122101-01</t>
+  </si>
+  <si>
+    <t>T122127-01</t>
+  </si>
+  <si>
+    <t>T122128-01</t>
+  </si>
+  <si>
+    <t>T122129-01</t>
+  </si>
+  <si>
+    <t>T122139-01</t>
+  </si>
+  <si>
+    <t>T122182-01</t>
+  </si>
+  <si>
+    <t>T122183-01</t>
+  </si>
+  <si>
+    <t>T122184-01</t>
+  </si>
+  <si>
+    <t>T122197-01</t>
+  </si>
+  <si>
+    <t>T122198-01</t>
+  </si>
+  <si>
+    <t>T122199-01</t>
+  </si>
+  <si>
+    <t>T122224-01</t>
+  </si>
+  <si>
+    <t>T122225-01</t>
+  </si>
+  <si>
+    <t>T122226-01</t>
+  </si>
+  <si>
+    <t>T122261-01</t>
+  </si>
+  <si>
+    <t>T122267-01</t>
+  </si>
+  <si>
+    <t>T122371-01</t>
+  </si>
+  <si>
+    <t>T122386-01</t>
+  </si>
+  <si>
+    <t>T122548-01</t>
+  </si>
+  <si>
+    <t>T122550-01</t>
+  </si>
+  <si>
+    <t>T122552-01</t>
+  </si>
+  <si>
+    <t>T122554-01</t>
+  </si>
+  <si>
+    <t>T122558-01</t>
+  </si>
+  <si>
+    <t>T122626-01</t>
+  </si>
+  <si>
+    <t>T122627-01</t>
+  </si>
+  <si>
+    <t>T122628-01</t>
+  </si>
+  <si>
+    <t>T122629-01</t>
+  </si>
+  <si>
+    <t>T122630-01</t>
+  </si>
+  <si>
+    <t>T122631-01</t>
+  </si>
+  <si>
+    <t>T122635-01</t>
+  </si>
+  <si>
+    <t>T122637-01</t>
+  </si>
+  <si>
+    <t>T122640-01</t>
+  </si>
+  <si>
+    <t>T122642-01</t>
+  </si>
+  <si>
+    <t>T122701-01</t>
+  </si>
+  <si>
+    <t>T122857-01</t>
+  </si>
+  <si>
+    <t>T122880-01</t>
+  </si>
+  <si>
+    <t>T122881-01</t>
+  </si>
+  <si>
+    <t>T122887-01</t>
+  </si>
+  <si>
+    <t>T122892-01</t>
+  </si>
+  <si>
+    <t>T122896-01</t>
+  </si>
+  <si>
+    <t>T122913-01</t>
+  </si>
+  <si>
+    <t>T122914-01</t>
+  </si>
+  <si>
+    <t>T122915-01</t>
+  </si>
+  <si>
+    <t>T122957-01</t>
+  </si>
+  <si>
+    <t>T122958-01</t>
+  </si>
+  <si>
+    <t>T122959-01</t>
+  </si>
+  <si>
+    <t>T122960-01</t>
+  </si>
+  <si>
+    <t>T122961-01</t>
+  </si>
+  <si>
+    <t>T122962-01</t>
+  </si>
+  <si>
+    <t>T123103-01</t>
+  </si>
+  <si>
+    <t>T123104-01</t>
+  </si>
+  <si>
+    <t>T123105-01</t>
+  </si>
+  <si>
+    <t>T123118-01</t>
+  </si>
+  <si>
+    <t>T123123-01</t>
+  </si>
+  <si>
+    <t>T123124-01</t>
+  </si>
+  <si>
+    <t>T123175-01</t>
+  </si>
+  <si>
+    <t>T123176-01</t>
+  </si>
+  <si>
+    <t>T123187-01</t>
+  </si>
+  <si>
+    <t>T123188-01</t>
+  </si>
+  <si>
+    <t>T123189-01</t>
+  </si>
+  <si>
+    <t>T123194-01</t>
+  </si>
+  <si>
+    <t>T123197-01</t>
+  </si>
+  <si>
+    <t>T123203-01</t>
+  </si>
+  <si>
+    <t>T123225-01</t>
+  </si>
+  <si>
+    <t>T123241-01</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,81 +389,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,159 +693,533 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:A105"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>TradeId</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>T004521-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>T004724-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>T004572-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>T004724-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>T106729-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>T106749-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>T004563-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>T004676-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>T004675-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>T004457-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>T004483-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>T004485-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>T004488-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>T004437-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>T004440-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>T004521-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>T004572-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>T004724-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>T004437-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>T004440-01</t>
-        </is>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A99" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A100" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A101" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105" s="1" t="s">
+        <v>104</v>
       </c>
     </row>
   </sheetData>
